--- a/results/reliability_eval/Llama-3-8B_P108_sample_30_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P108_sample_30_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6045029329847335</v>
+        <v>0.5110841331866407</v>
       </c>
       <c r="B2" t="n">
-        <v>0.665272975022986</v>
+        <v>0.6331411277400567</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6045029329847335</v>
+        <v>0.5110841331866407</v>
       </c>
       <c r="D2" t="n">
-        <v>0.665272975022986</v>
+        <v>0.6331411277400567</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3920082931236184</v>
+        <v>0.5020296672863159</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5207168968327928</v>
+        <v>0.6261288248451357</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9977747617600408</v>
+        <v>0.9935484822809835</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9980293914818938</v>
+        <v>0.995031583019897</v>
       </c>
       <c r="I2" t="n">
-        <v>0.599</v>
+        <v>0.613</v>
       </c>
     </row>
   </sheetData>
